--- a/plantillas/consulta/Proyectos-GE.xlsx
+++ b/plantillas/consulta/Proyectos-GE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709A82B1-F656-4FCA-BEBC-12EE55710C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B60B484-FE9F-4ECE-92F4-1FF7A3FECA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -493,7 +493,7 @@
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
-    <row r="3" spans="1:10" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -533,17 +533,19 @@
       <c r="J7" s="4"/>
     </row>
     <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="I8" s="2" t="s">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
       <c r="B9" s="6"/>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="2"/>
+      <c r="J9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J9" s="4"/>
     </row>
     <row r="11" spans="1:10" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">

--- a/plantillas/consulta/Proyectos-GE.xlsx
+++ b/plantillas/consulta/Proyectos-GE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B60B484-FE9F-4ECE-92F4-1FF7A3FECA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB1D7B2-589A-4CC5-92C4-73D5E26EC896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -33,9 +33,6 @@
     <t>Hora:</t>
   </si>
   <si>
-    <t>Rubro General o Destino</t>
-  </si>
-  <si>
     <t>Opiniones por Mesa</t>
   </si>
   <si>
@@ -61,6 +58,9 @@
   </si>
   <si>
     <t>Clave de Proyecto</t>
+  </si>
+  <si>
+    <t>Destino de los recursos</t>
   </si>
 </sst>
 </file>
@@ -549,34 +549,34 @@
     </row>
     <row r="11" spans="1:10" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="I11" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/plantillas/consulta/Proyectos-GE.xlsx
+++ b/plantillas/consulta/Proyectos-GE.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB1D7B2-589A-4CC5-92C4-73D5E26EC896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
